--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -312,7 +312,7 @@
     <t>DiagnosticReport.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1072,23 +1072,358 @@
     <t>DiagnosticReport.presentedForm</t>
   </si>
   <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Entire report as issued</t>
+  </si>
+  <si>
+    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
+  </si>
+  <si>
+    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
+  </si>
+  <si>
+    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:title}
+</t>
+  </si>
+  <si>
+    <t>text (type=ED)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
     <t xml:space="preserve">Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
 </t>
   </si>
   <si>
-    <t>Entire report as issued</t>
-  </si>
-  <si>
-    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
-  </si>
-  <si>
-    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
-  </si>
-  <si>
-    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
-  </si>
-  <si>
-    <t>text (type=ED)</t>
+    <t>DiagnosticReport.presentedForm:report.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-tag}
+</t>
+  </si>
+  <si>
+    <t>Semantic categorization tag associated with the attachment</t>
+  </si>
+  <si>
+    <t>A categorization or semantic tag associated with an Attachment.
+This extension allows multiple tags to be associated with an
+Attachment for workflow, classification, indexing, retrieval,
+processing, or application behavior purposes.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+  </si>
+  <si>
+    <t>helperFile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-helperFile}
+</t>
+  </si>
+  <si>
+    <t>Helper file associated with the attachment</t>
+  </si>
+  <si>
+    <t>Provides the path or filename of an auxiliary/helper file required
+for interpretation, transformation, rendering, or processing of
+the attachment content.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Inline attachment data is prohibited</t>
+  </si>
+  <si>
+    <t>Inline binary data SHALL NOT be populated.
+Attachment content SHALL instead be persisted externally
+and referenced using Attachment.url.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Object storage path or external attachment location</t>
+  </si>
+  <si>
+    <t>Reference/path to the externally stored attachment content. Inline binary data in 
+Attachment.data SHALL NOT be populated. Inline content SHALL instead be persisted 
+externally, referenced using this url element, and tagged as 'inline-data-externalized-to-file'.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1390,11 +1725,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN34"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.36328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
@@ -1412,16 +1747,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="31.91796875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="53.48828125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.59765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5291,16 +5626,14 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>334</v>
@@ -5324,9 +5657,2993 @@
         <v>326</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="436">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1105,13 +1105,22 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.id</t>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.id</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension</t>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.extension</t>
@@ -1120,7 +1129,7 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
   </si>
   <si>
     <t>tag</t>
@@ -1139,7 +1148,7 @@
 processing, or application behavior purposes.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
   </si>
   <si>
     <t>helperFile</t>
@@ -1157,7 +1166,7 @@
 the attachment content.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.contentType</t>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.contentType</t>
@@ -1190,7 +1199,7 @@
     <t>./mediaType, ./charset</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.language</t>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.language</t>
@@ -1214,7 +1223,7 @@
     <t>./language</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.data</t>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.data</t>
@@ -1247,7 +1256,7 @@
     <t>./data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.url</t>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.url</t>
@@ -1283,7 +1292,7 @@
     <t>./reference/literal</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.size</t>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.size</t>
@@ -1311,7 +1320,7 @@
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.hash</t>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.hash</t>
@@ -1335,7 +1344,7 @@
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.title</t>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.title</t>
@@ -1350,6 +1359,9 @@
     <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>Official Corporate Logo</t>
   </si>
   <si>
@@ -1359,7 +1371,7 @@
     <t>./title/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.creation</t>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.creation</t>
@@ -1379,51 +1391,6 @@
   </si>
   <si>
     <t>Attachment.creation</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>Annotation/ notes associated with the diagnostic report</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.contentType</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.language</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.size</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.hash</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.title</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1725,10 +1692,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5786,9 +5753,11 @@
         <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5797,7 +5766,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5809,16 +5778,20 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>297</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5866,28 +5839,28 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5895,21 +5868,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5921,17 +5894,15 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5968,31 +5939,31 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6012,13 +5983,11 @@
         <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C38" t="s" s="2">
         <v>351</v>
       </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6037,15 +6006,17 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>352</v>
+        <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6082,16 +6053,16 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>304</v>
@@ -6115,7 +6086,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6123,13 +6094,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -6139,7 +6110,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6151,13 +6122,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6237,12 +6208,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6260,21 +6233,19 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>360</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6286,7 +6257,7 @@
         <v>20</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>20</v>
@@ -6298,13 +6269,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6322,28 +6293,28 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>369</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6351,10 +6322,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6380,14 +6351,14 @@
         <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6400,7 +6371,7 @@
         <v>20</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>20</v>
@@ -6412,13 +6383,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>114</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>115</v>
+        <v>370</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6436,7 +6407,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6454,10 +6425,10 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6465,10 +6436,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6479,7 +6450,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6488,22 +6459,20 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6516,7 +6485,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -6528,13 +6497,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6552,7 +6521,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6570,10 +6539,10 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6581,10 +6550,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6592,10 +6561,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6604,22 +6573,22 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6632,7 +6601,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -6668,7 +6637,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6686,10 +6655,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6697,10 +6666,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6708,7 +6677,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6723,19 +6692,19 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6748,7 +6717,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -6784,7 +6753,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6802,10 +6771,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6813,10 +6782,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6839,19 +6808,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6900,7 +6869,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6921,7 +6890,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6929,10 +6898,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6940,7 +6909,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -6955,17 +6924,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6975,10 +6946,10 @@
         <v>20</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -7014,7 +6985,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7035,7 +7006,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7043,10 +7014,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7054,7 +7025,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7069,17 +7040,17 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7089,10 +7060,10 @@
         <v>20</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7128,7 +7099,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7149,7 +7120,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7157,14 +7128,12 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7173,7 +7142,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7182,22 +7151,20 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>344</v>
+        <v>431</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7246,13 +7213,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>334</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7264,1386 +7231,12 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>341</v>
+        <v>411</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AN60" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,10 +608,12 @@
 </t>
   </si>
   <si>
-    <t>Service category</t>
-  </si>
-  <si>
-    <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
+    <t>Operational procedure/service categories</t>
+  </si>
+  <si>
+    <t>Broad and optional subcategory classifications used
+for workflow, routing, analytics, and operational
+grouping of DiagnosticReport resources.</t>
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
@@ -626,6 +628,10 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>OBR-24</t>
   </si>
   <si>
@@ -633,6 +639,38 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:broadCategory</t>
+  </si>
+  <si>
+    <t>broadCategory</t>
+  </si>
+  <si>
+    <t>Required broad procedure/service category</t>
+  </si>
+  <si>
+    <t>Top-level operational classification of the
+diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-broad-314e</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1692,12 +1730,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1720,7 +1758,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.48828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.59765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.36328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3353,7 +3391,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>79</v>
@@ -3415,16 +3453,14 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>185</v>
@@ -3445,25 +3481,27 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3485,12 +3523,14 @@
         <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3515,11 +3555,9 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
         <v>202</v>
       </c>
@@ -3539,13 +3577,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -3554,28 +3592,30 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3594,18 +3634,18 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3629,13 +3669,11 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3653,13 +3691,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -3668,32 +3706,32 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3708,20 +3746,16 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3745,13 +3779,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3769,10 +3803,10 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3784,28 +3818,28 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3824,19 +3858,17 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3885,7 +3917,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3900,28 +3932,28 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>238</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3940,19 +3972,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4001,7 +4033,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4016,35 +4048,35 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4056,19 +4088,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4117,13 +4149,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4132,35 +4164,35 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4172,19 +4204,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4233,13 +4265,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4248,10 +4280,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>258</v>
@@ -4262,14 +4294,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4285,22 +4317,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4349,7 +4381,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4364,28 +4396,28 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4401,22 +4433,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4465,7 +4497,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4480,24 +4512,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>20</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4520,18 +4552,20 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4579,7 +4613,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4597,10 +4631,10 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>287</v>
+        <v>226</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4608,14 +4642,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4631,20 +4665,22 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4693,7 +4729,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4711,10 +4747,10 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4722,10 +4758,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4736,7 +4772,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4748,15 +4784,17 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4805,19 +4843,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4826,7 +4864,7 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
@@ -4834,14 +4872,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4857,10 +4895,10 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>302</v>
@@ -4868,10 +4906,10 @@
       <c r="M28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4919,7 +4957,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4931,16 +4969,16 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4948,46 +4986,42 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5035,19 +5069,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5056,7 +5090,7 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5064,21 +5098,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5090,20 +5124,18 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5151,19 +5183,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5172,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5187,26 +5219,26 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>318</v>
@@ -5214,8 +5246,12 @@
       <c r="M31" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="N31" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5263,19 +5299,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5284,7 +5320,7 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>320</v>
+        <v>132</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5299,7 +5335,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5318,15 +5354,17 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>325</v>
       </c>
@@ -5395,10 +5433,10 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5406,10 +5444,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5417,10 +5455,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5429,10 +5467,10 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>328</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>329</v>
@@ -5465,13 +5503,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5489,13 +5527,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -5507,10 +5545,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5518,21 +5556,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5544,19 +5582,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5593,23 +5629,25 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5621,10 +5659,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5632,14 +5670,12 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5660,20 +5696,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>344</v>
+        <v>187</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5697,13 +5729,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5721,7 +5753,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5739,10 +5771,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5753,11 +5785,9 @@
         <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5778,19 +5808,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5827,19 +5857,17 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5857,10 +5885,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5868,12 +5896,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5882,7 +5912,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5894,16 +5924,20 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5951,28 +5985,28 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -5980,14 +6014,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6006,18 +6042,20 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>134</v>
+        <v>355</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6053,19 +6091,19 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6077,16 +6115,16 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6094,14 +6132,12 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6110,7 +6146,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6122,13 +6158,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6179,19 +6215,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6200,7 +6236,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6208,23 +6244,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6236,15 +6270,17 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>360</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6281,19 +6317,19 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6314,7 +6350,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6322,12 +6358,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6336,7 +6374,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6345,21 +6383,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>367</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6371,7 +6407,7 @@
         <v>20</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>20</v>
@@ -6383,13 +6419,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>369</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6407,28 +6443,28 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>315</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6436,12 +6472,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6459,21 +6497,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6485,7 +6521,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -6497,13 +6533,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6521,19 +6557,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6542,7 +6578,7 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6550,10 +6586,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6564,7 +6600,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6573,22 +6609,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6601,7 +6635,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -6613,13 +6647,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6637,7 +6671,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6655,10 +6689,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6666,10 +6700,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6677,7 +6711,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>89</v>
@@ -6692,19 +6726,17 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>394</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6717,7 +6749,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -6729,13 +6761,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6753,7 +6785,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6771,10 +6803,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>401</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6782,10 +6814,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6796,7 +6828,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6805,22 +6837,22 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6869,7 +6901,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6887,10 +6919,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6898,10 +6930,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6909,7 +6941,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -6924,19 +6956,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6949,7 +6981,7 @@
         <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -6985,7 +7017,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7003,10 +7035,10 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>412</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7014,10 +7046,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7025,7 +7057,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7040,17 +7072,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>296</v>
+        <v>416</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7060,10 +7094,10 @@
         <v>20</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7099,7 +7133,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7120,7 +7154,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7128,10 +7162,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7154,17 +7188,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7213,7 +7249,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7234,9 +7270,237 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -542,7 +542,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -711,7 +711,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -845,7 +845,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -895,7 +895,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -921,7 +921,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1054,7 +1054,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1743,7 +1743,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="134.265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
